--- a/log_push.xlsx
+++ b/log_push.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -932,6 +932,259 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-03-09 12:49:56</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TRT19</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0001263-34.2025.5.19.0003</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>processo não encontrado.
+x</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-03-09 12:51:27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TRT19</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0025800-57.1989.5.19.0003</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>o processo 0025800-57.1989.5.19.0003 já está cadastrado no push.
+x</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-16 11:55:22</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TRT5</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0000008-86.2026.5.05.0038</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>não foi possível confirmar inserção</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-19 11:20:28</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TRT7</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0001757-96.2025.5.07.0013</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>processo não encontrado.
+x</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-19 11:21:56</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TRT7</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0001286-51.2023.5.07.0013</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>processo não encontrado.
+x</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-20 16:23:29</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>19</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0001251-20.2025.5.19.0003</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exceção não tratada: Message: Failed to decode response from marionette
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-20 16:25:02</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TRT19</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0025800-57.1989.5.19.0003</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>o processo 0025800-57.1989.5.19.0003 já está cadastrado no push.
+x</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-25 13:06:39</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>19</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0000182-19.2026.5.19.0002</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exceção não tratada: Alert Text: Não foi possível encontrar o PJe Office.
+Message: Unexpected alert dialog detected. Performed handler "dismiss"
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+UnexpectedAlertOpenError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:927:5
+GeckoDriver.prototype._handleUserPrompts@chrome://remote/content/marionette/driver.sys.mjs:3371:11
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-26 10:31:48</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TRT6</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0000236-33.2022.5.06.0019</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>o processo 0000236-33.2022.5.06.0019 já está cadastrado no push.
+x</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/log_push.xlsx
+++ b/log_push.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1185,6 +1185,141 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-26 11:25:31</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TRT6</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0000822-39.2023.5.06.0018</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>registro inserido (validação por total: 3904)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26 11:27:22</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>TRT6</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0001057-41.2025.5.06.0016</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>registro inserido (validação por total: 3905)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-26 14:17:32</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TRT13</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0001184-20.2025.5.13.0004</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>registro inserido (validação por total: 895)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-03-26 14:44:28</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>TRT19</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0000382-26.2026.5.19.0002</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>registro inserido (validação por total: 265)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-03-26 15:30:56</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>TRT5</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0000596-06.2020.5.05.0038</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>registro inserido (validação por total: 170)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/log_push.xlsx
+++ b/log_push.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1320,6 +1320,1164 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-03-30 12:00:50</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>TRT19</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0000448-06.2026.5.19.0002</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>registro inserido (validação por total: 267)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-03-30 12:54:44</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>TRT9</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0000223-65.2026.5.09.0001</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>registro inserido (validação por total: 70)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-03-30 12:56:31</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>TRT9</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0001555-38.2024.5.09.0001</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>registro inserido (validação por total: 71)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-03-30 13:47:37</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>6</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0000097-24.2025.5.06.0101</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erro na automacao: Message: Element &lt;button class="mat-focus-indicator mat-tooltip-trigger float-right mr-10 mat-mini-fab mat-button-base mat-accent ng-star-inserted"&gt; is not clickable at point (97,156) because another element &lt;div class="cdk-overlay-backdrop cdk-overlay-dark-backdrop cdk-overlay-backdrop-showing"&gt; obscures it; For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#elementclickinterceptedexception
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+ElementClickInterceptedError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:354:5
+webdriverClickElement@chrome://remote/content/marionette/interaction.sys.mjs:175:11
+interaction.clickElement@chrome://remote/content/marionette/interaction.sys.mjs:134:11
+clickElement@chrome://remote/content/marionette/actors/MarionetteCommandsChild.sys.mjs:326:29
+receiveMessage@chrome://remote/content/marionette/actors/MarionetteCommandsChild.sys.mjs:205:31
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-03-30 13:49:09</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>TRT6</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0000866-71.2021.5.06.0101</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>processo não encontrado.
+x</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-03-30 14:03:18</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>TRT13</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0001233-20.2024.5.13.0029</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>processo não encontrado.
+x</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-03-30 14:03:55</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>13</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0000018-09.2024.5.13.0029</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erro na automacao: Alert Text: Não foi possível encontrar o PJe Office.
+Message: Unexpected alert dialog detected. Performed handler "dismiss"
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+UnexpectedAlertOpenError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:927:5
+GeckoDriver.prototype._handleUserPrompts@chrome://remote/content/marionette/driver.sys.mjs:3371:11
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-03-30 14:17:35</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>6</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0000233-61.2025.5.06.0023</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erro na automacao: Alert Text: Não foi possível encontrar o PJe Office.
+Message: Unexpected alert dialog detected. Performed handler "dismiss"
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+UnexpectedAlertOpenError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:927:5
+GeckoDriver.prototype._handleUserPrompts@chrome://remote/content/marionette/driver.sys.mjs:3371:11
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-03-30 14:39:02</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0100544-47.2021.5.01.0247</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erro na automacao: Alert Text: Não foi possível encontrar o PJe Office.
+Message: Unexpected alert dialog detected. Performed handler "dismiss"
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+UnexpectedAlertOpenError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:927:5
+GeckoDriver.prototype._handleUserPrompts@chrome://remote/content/marionette/driver.sys.mjs:3371:11
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:49:34</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>6</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>0000514-29.2024.5.06.0192</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erro na automacao: Message: Element &lt;button class="mat-focus-indicator mat-tooltip-trigger float-right mr-10 mat-mini-fab mat-button-base mat-accent ng-star-inserted"&gt; is not clickable at point (1890,99) because another element &lt;div class="cdk-overlay-backdrop cdk-overlay-dark-backdrop cdk-overlay-backdrop-showing"&gt; obscures it; For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#elementclickinterceptedexception
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+ElementClickInterceptedError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:354:5
+webdriverClickElement@chrome://remote/content/marionette/interaction.sys.mjs:175:11
+interaction.clickElement@chrome://remote/content/marionette/interaction.sys.mjs:134:11
+clickElement@chrome://remote/content/marionette/actors/MarionetteCommandsChild.sys.mjs:326:29
+receiveMessage@chrome://remote/content/marionette/actors/MarionetteCommandsChild.sys.mjs:205:31
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:51:24</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>TRT6</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>0000300-98.2026.5.06.0311</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>registro inserido (validação por total: 3915)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:53:11</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>TRT6</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0001119-06.2024.5.06.0311</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>registro inserido (validação por total: 3916)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:53:49</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>6</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>0000932-74.2025.5.06.0145</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erro na automacao: Alert Text: Não foi possível encontrar o PJe Office.
+Message: Unexpected alert dialog detected. Performed handler "dismiss"
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+UnexpectedAlertOpenError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:927:5
+GeckoDriver.prototype._handleUserPrompts@chrome://remote/content/marionette/driver.sys.mjs:3371:11
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:54:25</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>9</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>0000231-13.2024.5.09.0001</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erro na automacao: Alert Text: Não foi possível encontrar o PJe Office.
+Message: Unexpected alert dialog detected. Performed handler "dismiss"
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+UnexpectedAlertOpenError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:927:5
+GeckoDriver.prototype._handleUserPrompts@chrome://remote/content/marionette/driver.sys.mjs:3371:11
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:55:02</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>13</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0001731-69.2025.5.13.0001</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erro na automacao: Alert Text: Não foi possível encontrar o PJe Office.
+Message: Unexpected alert dialog detected. Performed handler "dismiss"
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+UnexpectedAlertOpenError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:927:5
+GeckoDriver.prototype._handleUserPrompts@chrome://remote/content/marionette/driver.sys.mjs:3371:11
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:55:39</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>6</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0000479-66.2025.5.06.0311</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erro na automacao: Alert Text: Não foi possível encontrar o PJe Office.
+Message: Unexpected alert dialog detected. Performed handler "dismiss"
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+UnexpectedAlertOpenError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:927:5
+GeckoDriver.prototype._handleUserPrompts@chrome://remote/content/marionette/driver.sys.mjs:3371:11
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:56:16</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>6</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0000489-37.2025.5.06.0012</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erro na automacao: Alert Text: Não foi possível encontrar o PJe Office.
+Message: Unexpected alert dialog detected. Performed handler "dismiss"
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+UnexpectedAlertOpenError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:927:5
+GeckoDriver.prototype._handleUserPrompts@chrome://remote/content/marionette/driver.sys.mjs:3371:11
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:56:53</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>13</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0000599-68.2025.5.13.0003</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erro na automacao: Alert Text: Não foi possível encontrar o PJe Office.
+Message: Unexpected alert dialog detected. Performed handler "dismiss"
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+UnexpectedAlertOpenError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:927:5
+GeckoDriver.prototype._handleUserPrompts@chrome://remote/content/marionette/driver.sys.mjs:3371:11
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:57:29</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>13</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0001518-48.2025.5.13.0006</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erro na automacao: Alert Text: Não foi possível encontrar o PJe Office.
+Message: Unexpected alert dialog detected. Performed handler "dismiss"
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+UnexpectedAlertOpenError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:927:5
+GeckoDriver.prototype._handleUserPrompts@chrome://remote/content/marionette/driver.sys.mjs:3371:11
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:58:11</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>19</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0000892-67.2025.5.19.0004</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erro na automacao: Alert Text: Não foi possível encontrar o PJe Office.
+Message: Unexpected alert dialog detected. Performed handler "dismiss"
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+UnexpectedAlertOpenError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:927:5
+GeckoDriver.prototype._handleUserPrompts@chrome://remote/content/marionette/driver.sys.mjs:3371:11
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:58:47</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>13</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>0001373-41.2025.5.13.0022</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erro na automacao: Alert Text: Não foi possível encontrar o PJe Office.
+Message: Unexpected alert dialog detected. Performed handler "dismiss"
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+UnexpectedAlertOpenError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:927:5
+GeckoDriver.prototype._handleUserPrompts@chrome://remote/content/marionette/driver.sys.mjs:3371:11
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:59:25</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>19</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>0001083-84.2026.5.19.0002</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erro na automacao: Alert Text: Não foi possível encontrar o PJe Office.
+Message: Unexpected alert dialog detected. Performed handler "dismiss"
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+UnexpectedAlertOpenError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:927:5
+GeckoDriver.prototype._handleUserPrompts@chrome://remote/content/marionette/driver.sys.mjs:3371:11
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-03-31 16:00:01</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>10</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>0000854-07.2025.5.10.0101</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erro na automacao: Alert Text: Não foi possível encontrar o PJe Office.
+Message: Unexpected alert dialog detected. Performed handler "dismiss"
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+UnexpectedAlertOpenError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:927:5
+GeckoDriver.prototype._handleUserPrompts@chrome://remote/content/marionette/driver.sys.mjs:3371:11
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-03-31 16:00:39</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>10</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>0001058-49.2019.5.10.0008</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erro na automacao: Alert Text: Não foi possível encontrar o PJe Office.
+Message: Unexpected alert dialog detected. Performed handler "dismiss"
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+UnexpectedAlertOpenError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:927:5
+GeckoDriver.prototype._handleUserPrompts@chrome://remote/content/marionette/driver.sys.mjs:3371:11
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-03-31 16:01:16</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>13</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>0001685-65.2025.5.13.0006</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erro na automacao: Alert Text: Não foi possível encontrar o PJe Office.
+Message: Unexpected alert dialog detected. Performed handler "dismiss"
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+UnexpectedAlertOpenError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:927:5
+GeckoDriver.prototype._handleUserPrompts@chrome://remote/content/marionette/driver.sys.mjs:3371:11
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-03-31 16:01:56</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>10</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>0000895-65.2025.5.10.0006</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erro na automacao: Alert Text: Não foi possível encontrar o PJe Office.
+Message: Unexpected alert dialog detected. Performed handler "dismiss"
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+UnexpectedAlertOpenError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:927:5
+GeckoDriver.prototype._handleUserPrompts@chrome://remote/content/marionette/driver.sys.mjs:3371:11
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-03-31 16:02:36</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>19</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>0001036-13.2026.5.19.0002</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erro na automacao: Alert Text: Não foi possível encontrar o PJe Office.
+Message: Unexpected alert dialog detected. Performed handler "dismiss"
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+UnexpectedAlertOpenError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:927:5
+GeckoDriver.prototype._handleUserPrompts@chrome://remote/content/marionette/driver.sys.mjs:3371:11
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-03-31 16:04:44</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>6</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>0000028-28.2026.5.06.0013</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erro na automacao: Alert Text: Não foi possível encontrar o PJe Office.
+Message: Unexpected alert dialog detected. Performed handler "dismiss"
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+UnexpectedAlertOpenError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:927:5
+GeckoDriver.prototype._handleUserPrompts@chrome://remote/content/marionette/driver.sys.mjs:3371:11
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-03-31 17:03:30</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>TRT1</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>0100544-47.2021.5.01.0247</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>registro inserido (validação por total: 61)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-03-31 17:21:07</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>10</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>0001868-15.2024.5.10.0019</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erro na automacao: Message: Element &lt;button class="mat-focus-indicator mat-tooltip-trigger float-right mr-10 mat-mini-fab mat-button-base mat-accent ng-star-inserted"&gt; is not clickable at point (1890,99) because another element &lt;div class="cdk-overlay-backdrop cdk-overlay-dark-backdrop cdk-overlay-backdrop-showing"&gt; obscures it; For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#elementclickinterceptedexception
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+ElementClickInterceptedError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:354:5
+webdriverClickElement@chrome://remote/content/marionette/interaction.sys.mjs:175:11
+interaction.clickElement@chrome://remote/content/marionette/interaction.sys.mjs:134:11
+clickElement@chrome://remote/content/marionette/actors/MarionetteCommandsChild.sys.mjs:326:29
+receiveMessage@chrome://remote/content/marionette/actors/MarionetteCommandsChild.sys.mjs:205:31
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-04-01 09:30:36</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>6</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>0000915-55.2025.5.06.0010</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erro na automacao: Message: Element &lt;button class="mat-focus-indicator mat-tooltip-trigger float-right mr-10 mat-mini-fab mat-button-base mat-accent ng-star-inserted"&gt; is not clickable at point (1890,99) because another element &lt;div class="cdk-overlay-backdrop cdk-overlay-dark-backdrop cdk-overlay-backdrop-showing"&gt; obscures it; For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#elementclickinterceptedexception
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+ElementClickInterceptedError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:354:5
+webdriverClickElement@chrome://remote/content/marionette/interaction.sys.mjs:175:11
+interaction.clickElement@chrome://remote/content/marionette/interaction.sys.mjs:134:11
+clickElement@chrome://remote/content/marionette/actors/MarionetteCommandsChild.sys.mjs:326:29
+receiveMessage@chrome://remote/content/marionette/actors/MarionetteCommandsChild.sys.mjs:205:31
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:03:43</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>6</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>0000654-45.2024.5.06.0101</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erro na automacao: Message: Element &lt;button class="mat-focus-indicator mat-tooltip-trigger float-right mr-10 mat-mini-fab mat-button-base mat-accent ng-star-inserted"&gt; is not clickable at point (1890,99) because another element &lt;div class="cdk-overlay-backdrop cdk-overlay-dark-backdrop cdk-overlay-backdrop-showing"&gt; obscures it; For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#elementclickinterceptedexception
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+ElementClickInterceptedError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:354:5
+webdriverClickElement@chrome://remote/content/marionette/interaction.sys.mjs:175:11
+interaction.clickElement@chrome://remote/content/marionette/interaction.sys.mjs:134:11
+clickElement@chrome://remote/content/marionette/actors/MarionetteCommandsChild.sys.mjs:326:29
+receiveMessage@chrome://remote/content/marionette/actors/MarionetteCommandsChild.sys.mjs:205:31
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:28:36</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>6</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>0000479-21.2024.5.06.0014</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erro na automacao: Message: Element &lt;button class="mat-focus-indicator mat-tooltip-trigger float-right mr-10 mat-mini-fab mat-button-base mat-accent ng-star-inserted"&gt; is not clickable at point (1890,99) because another element &lt;div class="cdk-overlay-backdrop cdk-overlay-dark-backdrop cdk-overlay-backdrop-showing"&gt; obscures it; For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#elementclickinterceptedexception
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+ElementClickInterceptedError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:354:5
+webdriverClickElement@chrome://remote/content/marionette/interaction.sys.mjs:175:11
+interaction.clickElement@chrome://remote/content/marionette/interaction.sys.mjs:134:11
+clickElement@chrome://remote/content/marionette/actors/MarionetteCommandsChild.sys.mjs:326:29
+receiveMessage@chrome://remote/content/marionette/actors/MarionetteCommandsChild.sys.mjs:205:31
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-04-06 20:46:42</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>6</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>0001430-78.2025.5.06.0014</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erro na automacao: Message: Browsing context has been discarded
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+NoSuchWindowError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:782:5
+assert.that/&lt;@chrome://remote/content/shared/webdriver/Assert.sys.mjs:581:13
+assert.open@chrome://remote/content/shared/webdriver/Assert.sys.mjs:169:4
+GeckoDriver.prototype.maximizeWindow@chrome://remote/content/marionette/driver.sys.mjs:3154:15
+dispatch@chrome://remote/content/marionette/server.sys.mjs:318:40
+execute@chrome://remote/content/marionette/server.sys.mjs:289:16
+onPacket/&lt;@chrome://remote/content/marionette/server.sys.mjs:262:20
+onPacket@chrome://remote/content/marionette/server.sys.mjs:263:9
+_onJSONObjectReady/&lt;@chrome://remote/content/marionette/transport.sys.mjs:494:20
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-04-06 20:48:11</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>6</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>0000379-37.2022.5.06.0014</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erro na automacao: Message: Element &lt;button class="mat-focus-indicator mat-tooltip-trigger float-right mr-10 mat-mini-fab mat-button-base mat-accent ng-star-inserted"&gt; is not clickable at point (1890,99) because another element &lt;div class="cdk-overlay-backdrop cdk-overlay-dark-backdrop cdk-overlay-backdrop-showing"&gt; obscures it; For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#elementclickinterceptedexception
+Stacktrace:
+RemoteError@chrome://remote/content/shared/RemoteError.sys.mjs:8:8
+WebDriverError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:202:5
+ElementClickInterceptedError@chrome://remote/content/shared/webdriver/Errors.sys.mjs:354:5
+webdriverClickElement@chrome://remote/content/marionette/interaction.sys.mjs:175:11
+interaction.clickElement@chrome://remote/content/marionette/interaction.sys.mjs:134:11
+clickElement@chrome://remote/content/marionette/actors/MarionetteCommandsChild.sys.mjs:326:29
+receiveMessage@chrome://remote/content/marionette/actors/MarionetteCommandsChild.sys.mjs:205:31
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:14:40</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>TRT6</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>0001430-78.2025.5.06.0014</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>processo não encontrado.
+x</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-04-06 21:16:13</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>TRT6</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>0000379-37.2022.5.06.0014</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>processo não encontrado.
+x</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/log_push.xlsx
+++ b/log_push.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2478,6 +2478,56 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-05-06 18:20:28</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>13</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>0001281-88.2024.5.13.0025</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Erro interno na automacao</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-05-06 18:21:06</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>13</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>0021500-83.2013.5.13.0001</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Erro interno na automacao</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
